--- a/reports/pdf_rolling5_20261008.xlsx
+++ b/reports/pdf_rolling5_20261008.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,416억   ·   현금 2억(0.0%)      오늘 2026-10-08  vs  5일전 2026-09-30      매수 7종목  /  매도 23종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,326억   ·   현금 1억(0.0%)      오늘 2026-10-08  vs  5일전 2026-09-30      매수 7종목  /  매도 23종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>230</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3494713507</v>
+        <v>3519827067</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-219</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2418891083</v>
+        <v>-2436273614</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>123</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>10207134801</v>
+        <v>10280484875</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-73</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2349922113</v>
+        <v>-2366809023</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>87</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>4762277654</v>
+        <v>4796500129</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-56</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1559959073</v>
+        <v>-1571169184</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>28</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>552258238</v>
+        <v>556226853</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-46</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1462851231</v>
+        <v>-1473363510</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>27</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1044031050</v>
+        <v>1051533621</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-35</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1225536028</v>
+        <v>-1234342923</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1923845630</v>
+        <v>1937670686</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-31</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-475555705</v>
+        <v>-478973123</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>502584217</v>
+        <v>506195866</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-28</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-322355179</v>
+        <v>-324671674</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>-19</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-956760613</v>
+        <v>-963636045</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>-17</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-839490962</v>
+        <v>-845523676</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>-15</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-956955413</v>
+        <v>-963832245</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>-13</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-84455576</v>
+        <v>-85062487</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-278758920</v>
+        <v>-280762126</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1116,23 +1116,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1014616238</v>
+        <v>-1040252124</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.99%→0.84%</t>
+          <t>0.78%→0.55%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>42→31</t>
         </is>
       </c>
     </row>
@@ -1144,23 +1144,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1032830045</v>
+        <v>-1021907429</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.78%→0.55%</t>
+          <t>0.99%→0.84%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>42→31</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
         <v>-9</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-705663304</v>
+        <v>-710734312</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>-8</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-323368139</v>
+        <v>-325691914</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-490896212</v>
+        <v>-494423869</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-192949483</v>
+        <v>-194336048</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1284,23 +1284,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-140548261</v>
+        <v>-540923257</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.40%</t>
+          <t>0.49%→0.42%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1312,23 +1312,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-537063832</v>
+        <v>-141558262</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.49%→0.42%</t>
+          <t>0.44%→0.40%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
         <v>-5</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1251590540</v>
+        <v>-1260584666</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>-4</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-794784343</v>
+        <v>-800495788</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>-3</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-901437389</v>
+        <v>-907915259</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,499억   ·   현금 82억(2.3%)      오늘 2026-10-08  vs  5일전 2026-09-30      매수 8종목  /  매도 7종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,467억   ·   현금 55억(1.6%)      오늘 2026-10-08  vs  5일전 2026-09-30      매수 8종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1515,7 +1515,7 @@
         <v>122</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1726227128</v>
+        <v>1729509059</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>-258</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-2440030304</v>
+        <v>-2444669329</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>119</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>1746372932</v>
+        <v>1749693165</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>-233</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-941245619</v>
+        <v>-943035131</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>95</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>2233659425</v>
+        <v>2237906095</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>-122</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-1010709192</v>
+        <v>-1012630769</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>37</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>994508389</v>
+        <v>996399165</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>-70</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-942592179</v>
+        <v>-944384251</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>17</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>354997467</v>
+        <v>355672394</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>-20</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1014128193</v>
+        <v>-1016056270</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>13</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>313180460</v>
+        <v>313775883</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>-19</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-314811060</v>
+        <v>-315409584</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>10</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>965210184</v>
+        <v>967045257</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>-16</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-1032643396</v>
+        <v>-1034606675</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>4</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>308867259</v>
+        <v>309454482</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,947억   ·   현금 124억(4.3%)      오늘 2026-10-08  vs  5일전 2026-09-30      매수 1종목  /  매도 2종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,834억   ·   현금 83억(2.9%)      오늘 2026-10-08  vs  5일전 2026-09-30      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B42" s="4" t="n"/>
@@ -1940,7 +1940,7 @@
         <v>10</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>2095081138</v>
+        <v>2101400695</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>-197</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-1290437381</v>
+        <v>-1294329828</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>-26</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1251479480</v>
+        <v>-1255254415</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
     <row r="48" ht="19" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,198억   ·   현금 23억(1.0%)      오늘 2026-10-08  vs  5일전 2026-09-30      매수 3종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,225억   ·   현금 16억(0.7%)      오늘 2026-10-08  vs  5일전 2026-09-30      매수 3종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B48" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
         <v>295</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>4865819027</v>
+        <v>4984496736</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>-350</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-4985190540</v>
+        <v>-5106779730</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>279</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>3083382784</v>
+        <v>3158586733</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>-343</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-1493490762</v>
+        <v>-1529917119</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>221</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>2275217347</v>
+        <v>2330710077</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>-60</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-2134296231</v>
+        <v>-2186351884</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>-45</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-848515592</v>
+        <v>-869210954</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>-12</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-650030470</v>
+        <v>-665884765</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 325억   ·   현금 8억(2.5%)      오늘 2026-10-08  vs  5일전 2026-09-30      매수 6종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 315억   ·   현금 5억(1.7%)      오늘 2026-10-08  vs  5일전 2026-09-30      매수 6종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B57" s="4" t="n"/>
@@ -2378,7 +2378,7 @@
         <v>89</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>95500560</v>
+        <v>94411172</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
@@ -2399,11 +2399,11 @@
         <v>-209</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-171680960</v>
+        <v>-168838510</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>2.03%→1.51%</t>
+          <t>2.06%→1.53%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2422,11 +2422,11 @@
         <v>58</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>98008400</v>
+        <v>96825172</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>2.32%→2.63%</t>
+          <t>2.36%→2.68%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2443,11 +2443,11 @@
         <v>-60</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-61281600</v>
+        <v>-58343983</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>0.70%→0.51%</t>
+          <t>0.68%→0.50%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2466,11 +2466,11 @@
         <v>34</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>96757200</v>
+        <v>96410372</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.30%</t>
+          <t>0.00%→0.31%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -2487,11 +2487,11 @@
         <v>-34</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-99300400</v>
+        <v>-95485572</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>7.94%→7.67%</t>
+          <t>7.88%→7.61%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2510,7 +2510,7 @@
         <v>20</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>82144000</v>
+        <v>79559977</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
@@ -2531,11 +2531,11 @@
         <v>-15</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-95880000</v>
+        <v>-96593972</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>1.29%→0.99%</t>
+          <t>1.34%→1.03%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2554,11 +2554,11 @@
         <v>18</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>33109200</v>
+        <v>31823991</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>4.74%→4.86%</t>
+          <t>4.70%→4.82%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2575,11 +2575,11 @@
         <v>-14</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-39603200</v>
+        <v>-39031989</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>2.18%→2.07%</t>
+          <t>2.22%→2.10%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2598,11 +2598,11 @@
         <v>16</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>39984000</v>
+        <v>40854388</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>1.10%→1.23%</t>
+          <t>1.16%→1.29%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2619,11 +2619,11 @@
         <v>-7</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-33510400</v>
+        <v>-30701991</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>2.96%→2.87%</t>
+          <t>2.80%→2.71%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -2647,11 +2647,11 @@
         <v>-6</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-48960000</v>
+        <v>-44512787</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>2.42%→2.28%</t>
+          <t>2.27%→2.14%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2675,11 +2675,11 @@
         <v>-3</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-35985600</v>
+        <v>-33272390</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.57%</t>
+          <t>2.55%→2.45%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2708,7 +2708,7 @@
     <row r="71" ht="19" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,223억      오늘 2026-10-08  vs  5일전 2026-09-30      매수 0종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,210억      오늘 2026-10-08  vs  5일전 2026-09-30      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B71" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261008.xlsx
+++ b/reports/pdf_rolling5_20261008.xlsx
@@ -1116,23 +1116,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1040252124</v>
+        <v>-1021907429</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.78%→0.55%</t>
+          <t>0.99%→0.84%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>42→31</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -1144,23 +1144,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1021907429</v>
+        <v>-1040252124</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.99%→0.84%</t>
+          <t>0.78%→0.55%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>42→31</t>
         </is>
       </c>
     </row>
@@ -1228,23 +1228,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-494423869</v>
+        <v>-194336048</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.37%→0.33%</t>
+          <t>0.38%→0.39%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>32→25</t>
+          <t>81→74</t>
         </is>
       </c>
     </row>
@@ -1256,23 +1256,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-194336048</v>
+        <v>-494423869</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.39%</t>
+          <t>0.37%→0.33%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>81→74</t>
+          <t>32→25</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261008.xlsx
+++ b/reports/pdf_rolling5_20261008.xlsx
@@ -1116,23 +1116,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1021907429</v>
+        <v>-1040252124</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.99%→0.84%</t>
+          <t>0.78%→0.55%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>42→31</t>
         </is>
       </c>
     </row>
@@ -1144,23 +1144,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1040252124</v>
+        <v>-1021907429</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.78%→0.55%</t>
+          <t>0.99%→0.84%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>42→31</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -1228,23 +1228,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-194336048</v>
+        <v>-494423869</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.39%</t>
+          <t>0.37%→0.33%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>81→74</t>
+          <t>32→25</t>
         </is>
       </c>
     </row>
@@ -1256,23 +1256,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-494423869</v>
+        <v>-194336048</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.37%→0.33%</t>
+          <t>0.38%→0.39%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>32→25</t>
+          <t>81→74</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261008.xlsx
+++ b/reports/pdf_rolling5_20261008.xlsx
@@ -1116,23 +1116,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1021907429</v>
+        <v>-1040252124</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.99%→0.84%</t>
+          <t>0.78%→0.55%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>42→31</t>
         </is>
       </c>
     </row>
@@ -1144,23 +1144,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1040252124</v>
+        <v>-1021907429</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.78%→0.55%</t>
+          <t>0.99%→0.84%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>42→31</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
